--- a/data/excel/ot_firmas.xlsx
+++ b/data/excel/ot_firmas.xlsx
@@ -32,6 +32,15 @@
   </x:si>
   <x:si>
     <x:t>Comentario</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CodigoTarea</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scope</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SignatureImageDataUrl</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -406,9 +415,12 @@
     <x:col min="4" max="4" width="15.710625" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="13.710625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="11.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11.996339" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="6.139196" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="21.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:6">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -426,6 +438,15 @@
       </x:c>
       <x:c r="F1" s="1" t="s">
         <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
+        <x:v>8</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
